--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D138"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2317,9 +2317,23 @@
         <v/>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>2026-09-05</v>
+      </c>
+      <c r="B138" t="str">
+        <v>早</v>
+      </c>
+      <c r="C138">
+        <v>139.5</v>
+      </c>
+      <c r="D138" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D137"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D138"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D138"/>
+  <dimension ref="A1:D139"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2331,9 +2331,23 @@
         <v/>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>2026-09-06</v>
+      </c>
+      <c r="B139" t="str">
+        <v>早</v>
+      </c>
+      <c r="C139">
+        <v>138.9</v>
+      </c>
+      <c r="D139" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D138"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D139"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D139"/>
+  <dimension ref="A1:D140"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2345,9 +2345,23 @@
         <v/>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="B140" t="str">
+        <v>早</v>
+      </c>
+      <c r="C140">
+        <v>139.4</v>
+      </c>
+      <c r="D140" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D139"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D140"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D140"/>
+  <dimension ref="A1:D141"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2359,9 +2359,23 @@
         <v/>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="B141" t="str">
+        <v>早</v>
+      </c>
+      <c r="C141">
+        <v>139.8</v>
+      </c>
+      <c r="D141" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D140"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D141"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D141"/>
+  <dimension ref="A1:D142"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2373,9 +2373,23 @@
         <v/>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="B142" t="str">
+        <v>早</v>
+      </c>
+      <c r="C142">
+        <v>140.8</v>
+      </c>
+      <c r="D142" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D141"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D142"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D142"/>
+  <dimension ref="A1:D143"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2387,9 +2387,23 @@
         <v/>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>2026-09-10</v>
+      </c>
+      <c r="B143" t="str">
+        <v>早</v>
+      </c>
+      <c r="C143">
+        <v>142.9</v>
+      </c>
+      <c r="D143" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D142"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D143"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D143"/>
+  <dimension ref="A1:D144"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2401,9 +2401,23 @@
         <v/>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>2026-09-11</v>
+      </c>
+      <c r="B144" t="str">
+        <v>早</v>
+      </c>
+      <c r="C144">
+        <v>140.6</v>
+      </c>
+      <c r="D144" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D143"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D144"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D144"/>
+  <dimension ref="A1:D145"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2415,9 +2415,23 @@
         <v/>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>2026-09-12</v>
+      </c>
+      <c r="B145" t="str">
+        <v>中</v>
+      </c>
+      <c r="C145">
+        <v>141.3</v>
+      </c>
+      <c r="D145" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D144"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D145"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D145"/>
+  <dimension ref="A1:D146"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2429,9 +2429,23 @@
         <v/>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>2026-09-13</v>
+      </c>
+      <c r="B146" t="str">
+        <v>中</v>
+      </c>
+      <c r="C146">
+        <v>141.9</v>
+      </c>
+      <c r="D146" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D145"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D146"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D146"/>
+  <dimension ref="A1:D147"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2443,9 +2443,23 @@
         <v/>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="B147" t="str">
+        <v>早</v>
+      </c>
+      <c r="C147">
+        <v>143.2</v>
+      </c>
+      <c r="D147" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D146"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D147"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D147"/>
+  <dimension ref="A1:D148"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2457,9 +2457,23 @@
         <v/>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="B148" t="str">
+        <v>早</v>
+      </c>
+      <c r="C148">
+        <v>142.5</v>
+      </c>
+      <c r="D148" t="str">
+        <v>凌晨</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D147"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D148"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D148"/>
+  <dimension ref="A1:D149"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2471,9 +2471,23 @@
         <v>凌晨</v>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>2026-09-16</v>
+      </c>
+      <c r="B149" t="str">
+        <v>早</v>
+      </c>
+      <c r="C149">
+        <v>143</v>
+      </c>
+      <c r="D149" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D148"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D149"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D149"/>
+  <dimension ref="A1:D150"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2485,9 +2485,23 @@
         <v/>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>2026-09-17</v>
+      </c>
+      <c r="B150" t="str">
+        <v>早</v>
+      </c>
+      <c r="C150">
+        <v>142.9</v>
+      </c>
+      <c r="D150" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D149"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D150"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D150"/>
+  <dimension ref="A1:D151"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2499,9 +2499,23 @@
         <v/>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="B151" t="str">
+        <v>早</v>
+      </c>
+      <c r="C151">
+        <v>142.5</v>
+      </c>
+      <c r="D151" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D150"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D151"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D152"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2513,9 +2513,23 @@
         <v/>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>2026-09-20</v>
+      </c>
+      <c r="B152" t="str">
+        <v>早</v>
+      </c>
+      <c r="C152">
+        <v>144.4</v>
+      </c>
+      <c r="D152" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D151"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D152"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D152"/>
+  <dimension ref="A1:D153"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2527,9 +2527,23 @@
         <v/>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="B153" t="str">
+        <v>早</v>
+      </c>
+      <c r="C153">
+        <v>146.4</v>
+      </c>
+      <c r="D153" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D152"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D153"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D153"/>
+  <dimension ref="A1:D154"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2541,9 +2541,23 @@
         <v/>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>2026-09-22</v>
+      </c>
+      <c r="B154" t="str">
+        <v>早</v>
+      </c>
+      <c r="C154">
+        <v>144.3</v>
+      </c>
+      <c r="D154" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D153"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D154"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D154"/>
+  <dimension ref="A1:D155"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2555,9 +2555,23 @@
         <v/>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>2026-09-23</v>
+      </c>
+      <c r="B155" t="str">
+        <v>早</v>
+      </c>
+      <c r="C155">
+        <v>143.1</v>
+      </c>
+      <c r="D155" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D154"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D155"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D155"/>
+  <dimension ref="A1:D156"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2569,9 +2569,23 @@
         <v/>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>2026-09-24</v>
+      </c>
+      <c r="B156" t="str">
+        <v>早</v>
+      </c>
+      <c r="C156">
+        <v>144</v>
+      </c>
+      <c r="D156" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D155"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D156"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D156"/>
+  <dimension ref="A1:D157"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2583,9 +2583,23 @@
         <v/>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="B157" t="str">
+        <v>早</v>
+      </c>
+      <c r="C157">
+        <v>145.7</v>
+      </c>
+      <c r="D157" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D156"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D157"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D157"/>
+  <dimension ref="A1:D158"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2597,9 +2597,23 @@
         <v/>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="B158" t="str">
+        <v>早</v>
+      </c>
+      <c r="C158">
+        <v>142.4</v>
+      </c>
+      <c r="D158" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D157"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D158"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D158"/>
+  <dimension ref="A1:D159"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2611,9 +2611,23 @@
         <v/>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="B159" t="str">
+        <v>早</v>
+      </c>
+      <c r="C159">
+        <v>142</v>
+      </c>
+      <c r="D159" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D158"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D159"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D159"/>
+  <dimension ref="A1:D160"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2625,9 +2625,23 @@
         <v/>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="B160" t="str">
+        <v>中</v>
+      </c>
+      <c r="C160">
+        <v>141.6</v>
+      </c>
+      <c r="D160" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D159"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D160"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D160"/>
+  <dimension ref="A1:D161"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2639,9 +2639,23 @@
         <v/>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B161" t="str">
+        <v>中</v>
+      </c>
+      <c r="C161">
+        <v>142.1</v>
+      </c>
+      <c r="D161" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D160"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D161"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D162"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2653,9 +2653,23 @@
         <v/>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="B162" t="str">
+        <v>中</v>
+      </c>
+      <c r="C162">
+        <v>140.7</v>
+      </c>
+      <c r="D162" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D161"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D162"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D162"/>
+  <dimension ref="A1:D163"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2667,9 +2667,23 @@
         <v/>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>2026-10-06</v>
+      </c>
+      <c r="B163" t="str">
+        <v>中</v>
+      </c>
+      <c r="C163">
+        <v>141.4</v>
+      </c>
+      <c r="D163" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D162"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D163"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D163"/>
+  <dimension ref="A1:D164"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2681,9 +2681,23 @@
         <v/>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>2026-10-07</v>
+      </c>
+      <c r="B164" t="str">
+        <v>晚</v>
+      </c>
+      <c r="C164">
+        <v>142.7</v>
+      </c>
+      <c r="D164" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D163"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D164"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D164"/>
+  <dimension ref="A1:D165"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2695,9 +2695,23 @@
         <v/>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>2026-10-08</v>
+      </c>
+      <c r="B165" t="str">
+        <v>早</v>
+      </c>
+      <c r="C165">
+        <v>141.4</v>
+      </c>
+      <c r="D165" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D164"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D165"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D165"/>
+  <dimension ref="A1:D166"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2709,9 +2709,23 @@
         <v/>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>2026-10-09</v>
+      </c>
+      <c r="B166" t="str">
+        <v>早</v>
+      </c>
+      <c r="C166">
+        <v>141</v>
+      </c>
+      <c r="D166" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D165"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D166"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D166"/>
+  <dimension ref="A1:D167"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2723,9 +2723,23 @@
         <v/>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>2026-10-10</v>
+      </c>
+      <c r="B167" t="str">
+        <v>早</v>
+      </c>
+      <c r="C167">
+        <v>142.2</v>
+      </c>
+      <c r="D167" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D166"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D167"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D167"/>
+  <dimension ref="A1:D168"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2737,9 +2737,23 @@
         <v/>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="B168" t="str">
+        <v>早</v>
+      </c>
+      <c r="C168">
+        <v>142.7</v>
+      </c>
+      <c r="D168" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D167"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D168"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D168"/>
+  <dimension ref="A1:D169"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2751,9 +2751,23 @@
         <v/>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="B169" t="str">
+        <v>早</v>
+      </c>
+      <c r="C169">
+        <v>142.2</v>
+      </c>
+      <c r="D169" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D168"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D169"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D169"/>
+  <dimension ref="A1:D170"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2765,9 +2765,23 @@
         <v/>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="B170" t="str">
+        <v>早</v>
+      </c>
+      <c r="C170">
+        <v>141.9</v>
+      </c>
+      <c r="D170" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D169"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D170"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D170"/>
+  <dimension ref="A1:D171"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2779,9 +2779,23 @@
         <v/>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>2026-10-15</v>
+      </c>
+      <c r="B171" t="str">
+        <v>早</v>
+      </c>
+      <c r="C171">
+        <v>142.3</v>
+      </c>
+      <c r="D171" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D170"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D171"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D171"/>
+  <dimension ref="A1:D172"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2793,9 +2793,23 @@
         <v/>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>2026-10-16</v>
+      </c>
+      <c r="B172" t="str">
+        <v>早</v>
+      </c>
+      <c r="C172">
+        <v>143.1</v>
+      </c>
+      <c r="D172" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D171"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D172"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/weight.xlsx
+++ b/data/weight.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D172"/>
+  <dimension ref="A1:D173"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2807,9 +2807,23 @@
         <v/>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>2026-10-17</v>
+      </c>
+      <c r="B173" t="str">
+        <v>早</v>
+      </c>
+      <c r="C173">
+        <v>140.7</v>
+      </c>
+      <c r="D173" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D172"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D173"/>
   </ignoredErrors>
 </worksheet>
 </file>